--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_14_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_14_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>13.8</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="31">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>47.18</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>33.85</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>5.17</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>92.905</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>56.6523</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>60.98</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>36.2527</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>39.02</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2161,11 +2161,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>92.9437</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2284,6 +2284,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2579,6 +2580,7 @@
       <c r="F18" s="17" t="inlineStr"/>
       <c r="G18" s="17" t="inlineStr"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -2625,6 +2627,7 @@
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="120" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
@@ -3174,11 +3177,11 @@
       </c>
       <c r="B22" s="33">
         <f>SUM(B10:B21)</f>
-        <v/>
+        <v>853.87</v>
       </c>
       <c r="C22" s="23">
         <f>SUM(C10:C21)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
@@ -3188,19 +3191,19 @@
       <c r="E22" s="17" t="inlineStr"/>
       <c r="F22" s="17">
         <f>ROUND(AVERAGE(F10:F21),2)</f>
-        <v/>
+        <v>28.51</v>
       </c>
       <c r="G22" s="22">
         <f>ROUND(AVERAGE(G10:G21),4)</f>
-        <v/>
+        <v>0.5992</v>
       </c>
       <c r="H22" s="23">
         <f>ROUND(AVERAGE(H10:H21),2)</f>
-        <v/>
+        <v>71.82</v>
       </c>
       <c r="I22" s="23">
         <f>ROUND(AVERAGE(I10:I21),2)</f>
-        <v/>
+        <v>19.14</v>
       </c>
     </row>
     <row r="23"/>
@@ -3729,12 +3732,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>13 verificaciones</t>
+          <t>14 verificaciones</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>CONFORME: 6 · CORREGIDO: 1 · NO SUSTANTIVA: 4 · SUSTANTIVA: 2</t>
+          <t>CONFORME: 6 · CORREGIDO: 1 · NO SUSTANTIVA: 4 · SUSTANTIVA: 3</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
